--- a/AppliedStatistics/3.Measure_of_Central_Tendency.xlsx
+++ b/AppliedStatistics/3.Measure_of_Central_Tendency.xlsx
@@ -20,9 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t xml:space="preserve">Scores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median</t>
   </si>
   <si>
     <t xml:space="preserve">mode</t>
@@ -142,14 +148,35 @@
       <c r="A3" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="D3" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <f aca="false">AVERAGE(A2:A8)</f>
+        <v>9.42857142857143</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="D4" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <f aca="false">MEDIAN(A2:A8)</f>
+        <v>9</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <f aca="false">MODE(A2:A8)</f>
         <v>9</v>
       </c>
     </row>
@@ -161,13 +188,6 @@
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="n">
         <v>7</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="0" t="n">
-        <f aca="false">MODE(A2:A8)</f>
-        <v>9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
